--- a/artfynd/A 29517-2026 artfynd.xlsx
+++ b/artfynd/A 29517-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ68"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7579,10 +7579,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132888890</v>
+        <v>136547666</v>
       </c>
       <c r="B53" t="n">
-        <v>111153</v>
+        <v>99259</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7590,45 +7590,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220240</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lundagård, Jmt</t>
+          <t>Z727 Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>538302</v>
+        <v>538159</v>
       </c>
       <c r="R53" t="n">
-        <v>6999891</v>
+        <v>6999940</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7652,12 +7644,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7666,36 +7658,34 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Väg och Miljö AB, Elvira Klang</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132888890</t>
+          <t>https://artportalen.se/Sighting/136547666</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132888892</v>
+        <v>132888890</v>
       </c>
       <c r="B54" t="n">
         <v>111153</v>
@@ -7738,10 +7728,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>538262</v>
+        <v>538302</v>
       </c>
       <c r="R54" t="n">
-        <v>6999865</v>
+        <v>6999891</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7805,71 +7795,59 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132888892</t>
+          <t>https://artportalen.se/Sighting/132888890</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132888899</v>
+        <v>132888892</v>
       </c>
       <c r="B55" t="n">
-        <v>99195</v>
+        <v>111153</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lundagård, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>538365</v>
+        <v>538262</v>
       </c>
       <c r="R55" t="n">
-        <v>6999852</v>
+        <v>6999865</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7904,11 +7882,6 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Minst 14 plantor och 1 vinterståndare inom ca 1 m2 yta i tallskog.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7921,7 +7894,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7938,13 +7911,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132888899</t>
+          <t>https://artportalen.se/Sighting/132888892</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132888900</v>
+        <v>132888899</v>
       </c>
       <c r="B56" t="n">
         <v>99195</v>
@@ -7974,7 +7947,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7999,10 +7972,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>538401</v>
+        <v>538365</v>
       </c>
       <c r="R56" t="n">
-        <v>6999824</v>
+        <v>6999852</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -8039,7 +8012,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Minst 31 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 14 plantor och 1 vinterståndare inom ca 1 m2 yta i tallskog.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8054,12 +8027,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Gles gallrad barrblandskog.</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8076,13 +8044,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132888900</t>
+          <t>https://artportalen.se/Sighting/132888899</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132888901</v>
+        <v>132888900</v>
       </c>
       <c r="B57" t="n">
         <v>99195</v>
@@ -8112,7 +8080,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -8137,10 +8105,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>538445</v>
+        <v>538401</v>
       </c>
       <c r="R57" t="n">
-        <v>6999810</v>
+        <v>6999824</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8177,7 +8145,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta intill en rotvälta av gran i barrblandskog.</t>
+          <t>Minst 31 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8197,7 +8165,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Gles gallrad barrblandskog.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8214,13 +8182,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132888901</t>
+          <t>https://artportalen.se/Sighting/132888900</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132888902</v>
+        <v>132888901</v>
       </c>
       <c r="B58" t="n">
         <v>99195</v>
@@ -8250,7 +8218,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8275,10 +8243,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>538464</v>
+        <v>538445</v>
       </c>
       <c r="R58" t="n">
-        <v>6999815</v>
+        <v>6999810</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8315,7 +8283,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta intill en rotvälta av gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8335,7 +8303,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Gles och gallrad barrblandskog.</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8352,13 +8320,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132888902</t>
+          <t>https://artportalen.se/Sighting/132888901</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132888903</v>
+        <v>132888902</v>
       </c>
       <c r="B59" t="n">
         <v>99195</v>
@@ -8388,7 +8356,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -8413,10 +8381,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>538459</v>
+        <v>538464</v>
       </c>
       <c r="R59" t="n">
-        <v>6999844</v>
+        <v>6999815</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8453,7 +8421,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Minst 13 plantor och 2 vinterståndare inom ca 0,5 m2 yta.</t>
+          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8473,7 +8441,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Gles och gallrad barrblandskog.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8490,55 +8458,71 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132888903</t>
+          <t>https://artportalen.se/Sighting/132888902</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132888880</v>
+        <v>132888903</v>
       </c>
       <c r="B60" t="n">
-        <v>98060</v>
+        <v>99195</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lundagård, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>538372</v>
+        <v>538459</v>
       </c>
       <c r="R60" t="n">
-        <v>6999864</v>
+        <v>6999844</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8573,6 +8557,11 @@
           <t>2026-04-21</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Minst 13 plantor och 2 vinterståndare inom ca 0,5 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -8588,6 +8577,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
@@ -8602,16 +8596,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132888880</t>
+          <t>https://artportalen.se/Sighting/132888903</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132888912</v>
+        <v>132888880</v>
       </c>
       <c r="B61" t="n">
-        <v>101403</v>
+        <v>98060</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8619,30 +8613,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
@@ -8651,10 +8641,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>538473</v>
+        <v>538372</v>
       </c>
       <c r="R61" t="n">
-        <v>6999817</v>
+        <v>6999864</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8704,11 +8694,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
@@ -8723,13 +8708,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132888912</t>
+          <t>https://artportalen.se/Sighting/132888880</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132888913</v>
+        <v>132888912</v>
       </c>
       <c r="B62" t="n">
         <v>101403</v>
@@ -8772,10 +8757,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>538482</v>
+        <v>538473</v>
       </c>
       <c r="R62" t="n">
-        <v>6999837</v>
+        <v>6999817</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8844,16 +8829,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132888913</t>
+          <t>https://artportalen.se/Sighting/132888912</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132888895</v>
+        <v>132888913</v>
       </c>
       <c r="B63" t="n">
-        <v>96410</v>
+        <v>101403</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8861,26 +8846,30 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2812</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
@@ -8889,10 +8878,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>538579</v>
+        <v>538482</v>
       </c>
       <c r="R63" t="n">
-        <v>6999745</v>
+        <v>6999837</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8942,6 +8931,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
@@ -8956,43 +8950,44 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132888895</t>
+          <t>https://artportalen.se/Sighting/132888913</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132888909</v>
+        <v>132888895</v>
       </c>
       <c r="B64" t="n">
-        <v>79373</v>
+        <v>96410</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>2812</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -9000,10 +8995,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>538548</v>
+        <v>538579</v>
       </c>
       <c r="R64" t="n">
-        <v>6999791</v>
+        <v>6999745</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9053,26 +9048,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
@@ -9087,48 +9062,43 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132888909</t>
+          <t>https://artportalen.se/Sighting/132888895</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132888846</v>
+        <v>132888909</v>
       </c>
       <c r="B65" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -9136,10 +9106,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>538561</v>
+        <v>538548</v>
       </c>
       <c r="R65" t="n">
-        <v>6999707</v>
+        <v>6999791</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9174,17 +9144,13 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -9205,12 +9171,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9227,13 +9193,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132888846</t>
+          <t>https://artportalen.se/Sighting/132888909</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132888848</v>
+        <v>132888846</v>
       </c>
       <c r="B66" t="n">
         <v>57975</v>
@@ -9266,7 +9232,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -9276,10 +9242,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>538556</v>
+        <v>538561</v>
       </c>
       <c r="R66" t="n">
-        <v>6999706</v>
+        <v>6999707</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9316,7 +9282,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9367,48 +9333,48 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132888848</t>
+          <t>https://artportalen.se/Sighting/132888846</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132888889</v>
+        <v>132888848</v>
       </c>
       <c r="B67" t="n">
-        <v>111153</v>
+        <v>57975</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220240</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9416,10 +9382,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>538537</v>
+        <v>538556</v>
       </c>
       <c r="R67" t="n">
-        <v>6999795</v>
+        <v>6999706</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9454,19 +9420,43 @@
           <t>2026-04-21</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9483,16 +9473,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132888889</t>
+          <t>https://artportalen.se/Sighting/132888848</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132888879</v>
+        <v>132888889</v>
       </c>
       <c r="B68" t="n">
-        <v>98060</v>
+        <v>111153</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9500,16 +9490,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221945</v>
+        <v>220240</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -9519,7 +9509,11 @@
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
@@ -9528,10 +9522,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>538536</v>
+        <v>538537</v>
       </c>
       <c r="R68" t="n">
-        <v>6999797</v>
+        <v>6999795</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9594,6 +9588,118 @@
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888889</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>132888879</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lundagård, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>538536</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6999797</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132888879</t>
         </is>
@@ -9668,6 +9774,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29517-2026 artfynd.xlsx
+++ b/artfynd/A 29517-2026 artfynd.xlsx
@@ -7582,7 +7582,7 @@
         <v>136547666</v>
       </c>
       <c r="B53" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29517-2026 artfynd.xlsx
+++ b/artfynd/A 29517-2026 artfynd.xlsx
@@ -7582,7 +7582,7 @@
         <v>136547666</v>
       </c>
       <c r="B53" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29517-2026 artfynd.xlsx
+++ b/artfynd/A 29517-2026 artfynd.xlsx
@@ -7582,7 +7582,7 @@
         <v>136547666</v>
       </c>
       <c r="B53" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29517-2026 artfynd.xlsx
+++ b/artfynd/A 29517-2026 artfynd.xlsx
@@ -7582,7 +7582,7 @@
         <v>136547666</v>
       </c>
       <c r="B53" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29517-2026 artfynd.xlsx
+++ b/artfynd/A 29517-2026 artfynd.xlsx
@@ -7582,7 +7582,7 @@
         <v>136547666</v>
       </c>
       <c r="B53" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29517-2026 artfynd.xlsx
+++ b/artfynd/A 29517-2026 artfynd.xlsx
@@ -7582,7 +7582,7 @@
         <v>136547666</v>
       </c>
       <c r="B53" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29517-2026 artfynd.xlsx
+++ b/artfynd/A 29517-2026 artfynd.xlsx
@@ -7582,7 +7582,7 @@
         <v>136547666</v>
       </c>
       <c r="B53" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29517-2026 artfynd.xlsx
+++ b/artfynd/A 29517-2026 artfynd.xlsx
@@ -7582,7 +7582,7 @@
         <v>136547666</v>
       </c>
       <c r="B53" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29517-2026 artfynd.xlsx
+++ b/artfynd/A 29517-2026 artfynd.xlsx
@@ -7582,7 +7582,7 @@
         <v>136547666</v>
       </c>
       <c r="B53" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29517-2026 artfynd.xlsx
+++ b/artfynd/A 29517-2026 artfynd.xlsx
@@ -7582,7 +7582,7 @@
         <v>136547666</v>
       </c>
       <c r="B53" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29517-2026 artfynd.xlsx
+++ b/artfynd/A 29517-2026 artfynd.xlsx
@@ -7582,7 +7582,7 @@
         <v>136547666</v>
       </c>
       <c r="B53" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29517-2026 artfynd.xlsx
+++ b/artfynd/A 29517-2026 artfynd.xlsx
@@ -7582,7 +7582,7 @@
         <v>136547666</v>
       </c>
       <c r="B53" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 29517-2026 artfynd.xlsx
+++ b/artfynd/A 29517-2026 artfynd.xlsx
@@ -7582,7 +7582,7 @@
         <v>136547666</v>
       </c>
       <c r="B53" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
